--- a/AAII_Financials/Quarterly/TIMB_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/TIMB_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="145" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="149" uniqueCount="92">
   <si>
     <t>TIMB</t>
   </si>
@@ -656,429 +656,442 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AG102"/>
+  <dimension ref="A5:AH102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.140625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="22" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="26" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="30" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="32" max="32" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="33" max="33" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="34" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="19" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="23" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="27" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="31" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="33" max="33" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="34" max="34" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="35" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:34" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:34" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E7" s="2">
         <v>46112</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>46022</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45930</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45838</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45747</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45657</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45565</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45473</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>45382</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>45291</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>45199</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>45107</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>45016</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44926</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44834</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44742</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44651</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>44561</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>44469</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>44377</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>44286</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>44196</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>44104</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>44012</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43921</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43830</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>43738</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>43646</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AG7" s="2">
         <v>43555</v>
       </c>
-      <c r="AG7" s="2">
+      <c r="AH7" s="2">
         <v>43465</v>
       </c>
     </row>
-    <row r="8" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>1344500</v>
+      </c>
+      <c r="E8" s="3">
         <v>1304700</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>1256400</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>1259200</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>1211300</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>1115100</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>1072100</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>1178800</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>1135300</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>1215300</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>1293200</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>1212500</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>1216000</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>1113900</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>1046800</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>1036700</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>1075900</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>972100</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>968700</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>908700</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>853300</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>811900</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>915500</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>854600</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>1616400</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>752500</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AD8" s="3">
         <v>847100</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AE8" s="3">
         <v>813600</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AF8" s="3">
         <v>754800</v>
       </c>
-      <c r="AF8" s="3">
+      <c r="AG8" s="3">
         <v>784200</v>
       </c>
-      <c r="AG8" s="3">
+      <c r="AH8" s="3">
         <v>834100</v>
       </c>
     </row>
-    <row r="9" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>600400</v>
+      </c>
+      <c r="E9" s="3">
         <v>621500</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>557300</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>567700</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>566600</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>537900</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>495700</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>543500</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>525100</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>581700</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>600400</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>568400</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>608200</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>555300</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>658400</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>668500</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>697000</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>611500</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>563900</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>546100</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>522400</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Y9" s="3">
         <v>499800</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="Z9" s="3">
         <v>414300</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AA9" s="3">
         <v>399500</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AB9" s="3">
         <v>1122400</v>
       </c>
-      <c r="AB9" s="3">
+      <c r="AC9" s="3">
         <v>350200</v>
       </c>
-      <c r="AC9" s="3">
+      <c r="AD9" s="3">
         <v>307400</v>
       </c>
-      <c r="AD9" s="3">
+      <c r="AE9" s="3">
         <v>366300</v>
       </c>
-      <c r="AE9" s="3">
+      <c r="AF9" s="3">
         <v>329200</v>
       </c>
-      <c r="AF9" s="3">
+      <c r="AG9" s="3">
         <v>366300</v>
       </c>
-      <c r="AG9" s="3">
+      <c r="AH9" s="3">
         <v>367900</v>
       </c>
     </row>
-    <row r="10" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>744100</v>
+      </c>
+      <c r="E10" s="3">
         <v>683200</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>699000</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>691500</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>644700</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>577200</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>576500</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>635300</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>610200</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>633700</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>692800</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>644100</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>607800</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>558600</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>388500</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>368200</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>378900</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>360600</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>404800</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>362500</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>331000</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Y10" s="3">
         <v>312100</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="Z10" s="3">
         <v>501200</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AA10" s="3">
         <v>455100</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AB10" s="3">
         <v>494000</v>
       </c>
-      <c r="AB10" s="3">
+      <c r="AC10" s="3">
         <v>402400</v>
       </c>
-      <c r="AC10" s="3">
+      <c r="AD10" s="3">
         <v>539800</v>
       </c>
-      <c r="AD10" s="3">
+      <c r="AE10" s="3">
         <v>447200</v>
       </c>
-      <c r="AE10" s="3">
+      <c r="AF10" s="3">
         <v>425600</v>
       </c>
-      <c r="AF10" s="3">
+      <c r="AG10" s="3">
         <v>417900</v>
       </c>
-      <c r="AG10" s="3">
+      <c r="AH10" s="3">
         <v>466200</v>
       </c>
     </row>
-    <row r="11" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1112,8 +1125,9 @@
       <c r="AE11" s="3"/>
       <c r="AF11" s="3"/>
       <c r="AG11" s="3"/>
-    </row>
-    <row r="12" spans="1:33" x14ac:dyDescent="0.2">
+      <c r="AH11" s="3"/>
+    </row>
+    <row r="12" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
@@ -1207,8 +1221,11 @@
       <c r="AG12" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="13" spans="1:33" x14ac:dyDescent="0.2">
+      <c r="AH12" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="13" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1302,198 +1319,207 @@
       <c r="AG13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:33" x14ac:dyDescent="0.2">
+      <c r="AH13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="D14" s="3">
+      <c r="D14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E14" s="3">
         <v>21400</v>
       </c>
-      <c r="E14" s="3">
+      <c r="F14" s="3">
         <v>23700</v>
-      </c>
-      <c r="F14" s="3">
-        <v>200</v>
       </c>
       <c r="G14" s="3">
         <v>200</v>
       </c>
-      <c r="H14" s="3">
+      <c r="H14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I14" s="3">
         <v>10300</v>
       </c>
-      <c r="I14" s="3">
+      <c r="J14" s="3">
         <v>18500</v>
-      </c>
-      <c r="J14" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="K14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="L14" s="3">
+      <c r="L14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="M14" s="3">
         <v>16700</v>
       </c>
-      <c r="M14" s="3">
+      <c r="N14" s="3">
         <v>-36400</v>
-      </c>
-      <c r="N14" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="O14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="P14" s="3">
+      <c r="P14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q14" s="3">
         <v>41200</v>
       </c>
-      <c r="Q14" s="3">
+      <c r="R14" s="3">
         <v>6900</v>
       </c>
-      <c r="R14" s="3">
+      <c r="S14" s="3">
         <v>6700</v>
       </c>
-      <c r="S14" s="3">
+      <c r="T14" s="3">
         <v>4600</v>
       </c>
-      <c r="T14" s="3">
+      <c r="U14" s="3">
         <v>10000</v>
       </c>
-      <c r="U14" s="3">
+      <c r="V14" s="3">
         <v>7000</v>
       </c>
-      <c r="V14" s="3">
+      <c r="W14" s="3">
         <v>6700</v>
       </c>
-      <c r="W14" s="3">
+      <c r="X14" s="3">
         <v>13900</v>
       </c>
-      <c r="X14" s="3">
+      <c r="Y14" s="3">
         <v>9400</v>
       </c>
-      <c r="Y14" s="3">
+      <c r="Z14" s="3">
         <v>11700</v>
       </c>
-      <c r="Z14" s="3" t="s">
+      <c r="AA14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AA14" s="3">
+      <c r="AB14" s="3">
         <v>38400</v>
       </c>
-      <c r="AB14" s="3">
+      <c r="AC14" s="3">
         <v>11800</v>
       </c>
-      <c r="AC14" s="3">
+      <c r="AD14" s="3">
         <v>10700</v>
       </c>
-      <c r="AD14" s="3">
+      <c r="AE14" s="3">
         <v>17400</v>
       </c>
-      <c r="AE14" s="3">
+      <c r="AF14" s="3">
         <v>40300</v>
       </c>
-      <c r="AF14" s="3">
+      <c r="AG14" s="3">
         <v>16500</v>
       </c>
-      <c r="AG14" s="3">
+      <c r="AH14" s="3">
         <v>32600</v>
       </c>
     </row>
-    <row r="15" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>206400</v>
+      </c>
+      <c r="E15" s="3">
         <v>197200</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>197900</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>208200</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>203900</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>191400</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>172500</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>208700</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>193200</v>
       </c>
-      <c r="L15" s="3">
+      <c r="M15" s="3">
         <v>209000</v>
       </c>
-      <c r="M15" s="3">
+      <c r="N15" s="3">
         <v>194800</v>
       </c>
-      <c r="N15" s="3">
+      <c r="O15" s="3">
         <v>213200</v>
       </c>
-      <c r="O15" s="3">
+      <c r="P15" s="3">
         <v>205800</v>
       </c>
-      <c r="P15" s="3">
+      <c r="Q15" s="3">
         <v>177600</v>
       </c>
-      <c r="Q15" s="3">
+      <c r="R15" s="3">
         <v>32800</v>
       </c>
-      <c r="R15" s="3">
+      <c r="S15" s="3">
         <v>34700</v>
       </c>
-      <c r="S15" s="3">
+      <c r="T15" s="3">
         <v>37500</v>
       </c>
-      <c r="T15" s="3">
+      <c r="U15" s="3">
         <v>40200</v>
       </c>
-      <c r="U15" s="3">
+      <c r="V15" s="3">
         <v>41000</v>
       </c>
-      <c r="V15" s="3">
+      <c r="W15" s="3">
         <v>42200</v>
       </c>
-      <c r="W15" s="3">
+      <c r="X15" s="3">
         <v>40700</v>
       </c>
-      <c r="X15" s="3">
+      <c r="Y15" s="3">
         <v>41400</v>
       </c>
-      <c r="Y15" s="3">
+      <c r="Z15" s="3">
         <v>43800</v>
       </c>
-      <c r="Z15" s="3" t="s">
+      <c r="AA15" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AA15" s="3">
+      <c r="AB15" s="3">
         <v>48900</v>
       </c>
-      <c r="AB15" s="3">
+      <c r="AC15" s="3">
         <v>44300</v>
       </c>
-      <c r="AC15" s="3">
+      <c r="AD15" s="3">
         <v>43900</v>
       </c>
-      <c r="AD15" s="3">
+      <c r="AE15" s="3">
         <v>48900</v>
       </c>
-      <c r="AE15" s="3">
+      <c r="AF15" s="3">
         <v>44800</v>
       </c>
-      <c r="AF15" s="3">
+      <c r="AG15" s="3">
         <v>45900</v>
       </c>
-      <c r="AG15" s="3">
+      <c r="AH15" s="3">
         <v>39900</v>
       </c>
     </row>
-    <row r="16" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:34" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1524,198 +1550,205 @@
       <c r="AE16" s="3"/>
       <c r="AF16" s="3"/>
       <c r="AG16" s="3"/>
-    </row>
-    <row r="17" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH16" s="3"/>
+    </row>
+    <row r="17" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>1013000</v>
+      </c>
+      <c r="E17" s="3">
         <v>987500</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>910300</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>941800</v>
       </c>
-      <c r="G17" s="3">
-        <v>922100</v>
-      </c>
       <c r="H17" s="3">
+        <v>922300</v>
+      </c>
+      <c r="I17" s="3">
         <v>874800</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>802800</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>913300</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>883600</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>972300</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>993600</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>963500</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>995800</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>938400</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>872300</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>896000</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>929100</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>829200</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>616500</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>756600</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>724900</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>701100</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>724800</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>721600</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>1388200</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>660600</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>616100</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>690200</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AF17" s="3">
         <v>372700</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AG17" s="3">
         <v>700300</v>
       </c>
-      <c r="AG17" s="3">
+      <c r="AH17" s="3">
         <v>683600</v>
       </c>
     </row>
-    <row r="18" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>331500</v>
+      </c>
+      <c r="E18" s="3">
         <v>317100</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>346100</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>317500</v>
       </c>
-      <c r="G18" s="3">
-        <v>289100</v>
-      </c>
       <c r="H18" s="3">
+        <v>288900</v>
+      </c>
+      <c r="I18" s="3">
         <v>240300</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>269300</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>265500</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>251700</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>243100</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>299700</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>249000</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>220200</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>175500</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>174500</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>140800</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>146800</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>142900</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>352200</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>152100</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>128400</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>110900</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>190700</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>133000</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>228100</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>92000</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>231000</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AE18" s="3">
         <v>123400</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AF18" s="3">
         <v>382100</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AG18" s="3">
         <v>84000</v>
       </c>
-      <c r="AG18" s="3">
+      <c r="AH18" s="3">
         <v>150500</v>
       </c>
     </row>
-    <row r="19" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1749,483 +1782,499 @@
       <c r="AE19" s="3"/>
       <c r="AF19" s="3"/>
       <c r="AG19" s="3"/>
-    </row>
-    <row r="20" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH19" s="3"/>
+    </row>
+    <row r="20" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>4400</v>
+      </c>
+      <c r="E20" s="3">
         <v>30300</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>-4400</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>4800</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>14300</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>45900</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>3600</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>2700</v>
       </c>
-      <c r="K20" s="3">
-        <v>0</v>
-      </c>
       <c r="L20" s="3">
+        <v>0</v>
+      </c>
+      <c r="M20" s="3">
         <v>32300</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>22700</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>3700</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>4900</v>
       </c>
-      <c r="P20" s="3">
-        <v>0</v>
-      </c>
       <c r="Q20" s="3">
+        <v>0</v>
+      </c>
+      <c r="R20" s="3">
         <v>4600</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>2800</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>-20100</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>7400</v>
       </c>
-      <c r="U20" s="3">
+      <c r="V20" s="3">
         <v>20300</v>
       </c>
-      <c r="V20" s="3">
+      <c r="W20" s="3">
         <v>5400</v>
       </c>
-      <c r="W20" s="3">
+      <c r="X20" s="3">
         <v>36500</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Y20" s="3">
         <v>-4600</v>
       </c>
-      <c r="Y20" s="3">
+      <c r="Z20" s="3">
         <v>29500</v>
       </c>
-      <c r="Z20" s="3">
+      <c r="AA20" s="3">
         <v>-47500</v>
       </c>
-      <c r="AA20" s="3">
+      <c r="AB20" s="3">
         <v>-56900</v>
       </c>
-      <c r="AB20" s="3">
+      <c r="AC20" s="3">
         <v>-9700</v>
       </c>
-      <c r="AC20" s="3">
+      <c r="AD20" s="3">
         <v>600</v>
       </c>
-      <c r="AD20" s="3">
+      <c r="AE20" s="3">
         <v>-4600</v>
       </c>
-      <c r="AE20" s="3">
+      <c r="AF20" s="3">
         <v>179600</v>
       </c>
-      <c r="AF20" s="3">
+      <c r="AG20" s="3">
         <v>-6300</v>
       </c>
-      <c r="AG20" s="3">
+      <c r="AH20" s="3">
         <v>3400</v>
       </c>
     </row>
-    <row r="21" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>533500</v>
+      </c>
+      <c r="E21" s="3">
         <v>484000</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>548400</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>520900</v>
       </c>
-      <c r="G21" s="3">
-        <v>478700</v>
-      </c>
       <c r="H21" s="3">
+        <v>478500</v>
+      </c>
+      <c r="I21" s="3">
         <v>385800</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>438200</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>471500</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>444900</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>419700</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>471800</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>458500</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>421000</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>353100</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>513100</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>491000</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>465200</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>438000</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>662400</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>440200</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>440600</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>373400</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>490000</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3">
         <v>356300</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AB21" s="3">
         <v>714700</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AC21" s="3">
         <v>333700</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AD21" s="3">
         <v>427400</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AE21" s="3">
         <v>388300</v>
       </c>
-      <c r="AE21" s="3">
+      <c r="AF21" s="3">
         <v>791500</v>
       </c>
-      <c r="AF21" s="3">
+      <c r="AG21" s="3">
         <v>327300</v>
       </c>
-      <c r="AG21" s="3">
+      <c r="AH21" s="3">
         <v>344400</v>
       </c>
     </row>
-    <row r="22" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>292000</v>
+      </c>
+      <c r="E22" s="3">
         <v>137400</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
         <v>122300</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>165900</v>
       </c>
-      <c r="G22" s="3">
+      <c r="H22" s="3">
         <v>144800</v>
       </c>
-      <c r="H22" s="3">
+      <c r="I22" s="3">
         <v>110400</v>
       </c>
-      <c r="I22" s="3">
+      <c r="J22" s="3">
         <v>98300</v>
       </c>
-      <c r="J22" s="3">
+      <c r="K22" s="3">
         <v>128600</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>119100</v>
       </c>
-      <c r="L22" s="3">
+      <c r="M22" s="3">
         <v>117200</v>
       </c>
-      <c r="M22" s="3">
+      <c r="N22" s="3">
         <v>121600</v>
       </c>
-      <c r="N22" s="3">
+      <c r="O22" s="3">
         <v>135000</v>
       </c>
-      <c r="O22" s="3">
+      <c r="P22" s="3">
         <v>153700</v>
       </c>
-      <c r="P22" s="3">
+      <c r="Q22" s="3">
         <v>83200</v>
       </c>
-      <c r="Q22" s="3">
+      <c r="R22" s="3">
         <v>67500</v>
       </c>
-      <c r="R22" s="3">
+      <c r="S22" s="3">
         <v>77100</v>
       </c>
-      <c r="S22" s="3">
+      <c r="T22" s="3">
         <v>67900</v>
       </c>
-      <c r="T22" s="3">
+      <c r="U22" s="3">
         <v>58300</v>
       </c>
-      <c r="U22" s="3">
+      <c r="V22" s="3">
         <v>56700</v>
       </c>
-      <c r="V22" s="3">
+      <c r="W22" s="3">
         <v>47900</v>
       </c>
-      <c r="W22" s="3">
+      <c r="X22" s="3">
         <v>43500</v>
       </c>
-      <c r="X22" s="3">
+      <c r="Y22" s="3">
         <v>37600</v>
       </c>
-      <c r="Y22" s="3">
+      <c r="Z22" s="3">
         <v>38200</v>
       </c>
-      <c r="Z22" s="3" t="s">
+      <c r="AA22" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AA22" s="3">
+      <c r="AB22" s="3">
         <v>45400</v>
       </c>
-      <c r="AB22" s="3">
+      <c r="AC22" s="3">
         <v>35700</v>
       </c>
-      <c r="AC22" s="3">
+      <c r="AD22" s="3">
         <v>44100</v>
       </c>
-      <c r="AD22" s="3">
+      <c r="AE22" s="3">
         <v>45500</v>
       </c>
-      <c r="AE22" s="3">
+      <c r="AF22" s="3">
         <v>40300</v>
       </c>
-      <c r="AF22" s="3">
+      <c r="AG22" s="3">
         <v>42800</v>
       </c>
-      <c r="AG22" s="3">
+      <c r="AH22" s="3">
         <v>14300</v>
       </c>
     </row>
-    <row r="23" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>218500</v>
+      </c>
+      <c r="E23" s="3">
         <v>188800</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>267200</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>229000</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>215400</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>121000</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>184100</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>178500</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>166500</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>117200</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>247800</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>162700</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>127100</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>109800</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>111600</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>66500</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>58800</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>91900</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>315800</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>109600</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>121400</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>68700</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>182000</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>85500</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>125800</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>46500</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>187500</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>73300</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AF23" s="3">
         <v>521300</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AG23" s="3">
         <v>34800</v>
       </c>
-      <c r="AG23" s="3">
+      <c r="AH23" s="3">
         <v>139700</v>
       </c>
     </row>
-    <row r="24" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>31400</v>
+      </c>
+      <c r="E24" s="3">
         <v>32100</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>25500</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>2400</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>36400</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>-18100</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>14600</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>30600</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>25800</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>13700</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>24700</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>19300</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>-2800</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>28400</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>14900</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>-16200</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>2800</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>8500</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>110900</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>-90300</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>-8800</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Y24" s="3">
         <v>16900</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="Z24" s="3">
         <v>-16300</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AA24" s="3">
         <v>9600</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AB24" s="3">
         <v>39000</v>
       </c>
-      <c r="AB24" s="3">
+      <c r="AC24" s="3">
         <v>17600</v>
       </c>
-      <c r="AC24" s="3">
+      <c r="AD24" s="3">
         <v>17800</v>
       </c>
-      <c r="AD24" s="3">
+      <c r="AE24" s="3">
         <v>-32100</v>
       </c>
-      <c r="AE24" s="3">
+      <c r="AF24" s="3">
         <v>163300</v>
       </c>
-      <c r="AF24" s="3">
+      <c r="AG24" s="3">
         <v>12400</v>
       </c>
-      <c r="AG24" s="3">
+      <c r="AH24" s="3">
         <v>21400</v>
       </c>
     </row>
-    <row r="25" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2319,198 +2368,207 @@
       <c r="AG25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>187100</v>
+      </c>
+      <c r="E26" s="3">
         <v>156600</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>241700</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>226600</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>179000</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>139100</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>169500</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>147800</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>140700</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>103600</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>223100</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>143400</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>129900</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>81500</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>96700</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>82700</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>56000</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>83400</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>204900</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>199900</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>130200</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>51800</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>198300</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>76000</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>86800</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>28900</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>169600</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AE26" s="3">
         <v>105400</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AF26" s="3">
         <v>358100</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AG26" s="3">
         <v>22500</v>
       </c>
-      <c r="AG26" s="3">
+      <c r="AH26" s="3">
         <v>118300</v>
       </c>
     </row>
-    <row r="27" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>187100</v>
+      </c>
+      <c r="E27" s="3">
         <v>156600</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>241700</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>226600</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>179000</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>139100</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>169500</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>147800</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>140700</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>103600</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>223100</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>143400</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>129900</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>81500</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>96700</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>82700</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>56000</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>83400</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>204900</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>199900</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>130200</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>51800</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>198300</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>76000</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>86800</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>28900</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>169600</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AE27" s="3">
         <v>105400</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AF27" s="3">
         <v>358100</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AG27" s="3">
         <v>22500</v>
       </c>
-      <c r="AG27" s="3">
+      <c r="AH27" s="3">
         <v>118300</v>
       </c>
     </row>
-    <row r="28" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2604,8 +2662,11 @@
       <c r="AG28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2699,8 +2760,11 @@
       <c r="AG29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2794,8 +2858,11 @@
       <c r="AG30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2889,198 +2956,207 @@
       <c r="AG31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>-4400</v>
+      </c>
+      <c r="E32" s="3">
         <v>-30300</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>4400</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>-4800</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>-14300</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>-45900</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>-3600</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>-2700</v>
       </c>
-      <c r="K32" s="3">
-        <v>0</v>
-      </c>
       <c r="L32" s="3">
+        <v>0</v>
+      </c>
+      <c r="M32" s="3">
         <v>-32300</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>-22700</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>-3700</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>-4900</v>
       </c>
-      <c r="P32" s="3">
-        <v>0</v>
-      </c>
       <c r="Q32" s="3">
+        <v>0</v>
+      </c>
+      <c r="R32" s="3">
         <v>-4600</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>-2800</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>20100</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>-7400</v>
       </c>
-      <c r="U32" s="3">
+      <c r="V32" s="3">
         <v>-20300</v>
       </c>
-      <c r="V32" s="3">
+      <c r="W32" s="3">
         <v>-5400</v>
       </c>
-      <c r="W32" s="3">
+      <c r="X32" s="3">
         <v>-36500</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Y32" s="3">
         <v>4600</v>
       </c>
-      <c r="Y32" s="3">
+      <c r="Z32" s="3">
         <v>-29500</v>
       </c>
-      <c r="Z32" s="3">
+      <c r="AA32" s="3">
         <v>47500</v>
       </c>
-      <c r="AA32" s="3">
+      <c r="AB32" s="3">
         <v>56900</v>
       </c>
-      <c r="AB32" s="3">
+      <c r="AC32" s="3">
         <v>9700</v>
       </c>
-      <c r="AC32" s="3">
+      <c r="AD32" s="3">
         <v>-600</v>
       </c>
-      <c r="AD32" s="3">
+      <c r="AE32" s="3">
         <v>4600</v>
       </c>
-      <c r="AE32" s="3">
+      <c r="AF32" s="3">
         <v>-179600</v>
       </c>
-      <c r="AF32" s="3">
+      <c r="AG32" s="3">
         <v>6300</v>
       </c>
-      <c r="AG32" s="3">
+      <c r="AH32" s="3">
         <v>-3400</v>
       </c>
     </row>
-    <row r="33" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>187100</v>
+      </c>
+      <c r="E33" s="3">
         <v>156600</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>241700</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>226600</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>179000</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>139100</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>169500</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>147800</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>140700</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>103600</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>223100</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>143400</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>129900</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>81500</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>96700</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>82700</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>56000</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>83400</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>204900</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>199900</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>130200</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>51800</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>198300</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>76000</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>86800</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>28900</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>169600</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AE33" s="3">
         <v>105400</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AF33" s="3">
         <v>358100</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AG33" s="3">
         <v>22500</v>
       </c>
-      <c r="AG33" s="3">
+      <c r="AH33" s="3">
         <v>118300</v>
       </c>
     </row>
-    <row r="34" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3174,203 +3250,212 @@
       <c r="AG34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>187100</v>
+      </c>
+      <c r="E35" s="3">
         <v>156600</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>241700</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>226600</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>179000</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>139100</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>169500</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>147800</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>140700</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>103600</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>223100</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>143400</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>129900</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>81500</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>96700</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>82700</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>56000</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>83400</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>204900</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>199900</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>130200</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>51800</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>198300</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>76000</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>86800</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>28900</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>169600</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AE35" s="3">
         <v>105400</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AF35" s="3">
         <v>358100</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AG35" s="3">
         <v>22500</v>
       </c>
-      <c r="AG35" s="3">
+      <c r="AH35" s="3">
         <v>118300</v>
       </c>
     </row>
-    <row r="37" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:34" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E38" s="2">
         <v>46112</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>46022</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45930</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45838</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45747</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45657</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45565</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45473</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>45382</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>45291</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>45199</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>45107</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>45016</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44926</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44834</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44742</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44651</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>44561</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>44469</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>44377</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>44286</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>44196</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>44104</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>44012</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43921</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43830</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>43738</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>43646</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AG38" s="2">
         <v>43555</v>
       </c>
-      <c r="AG38" s="2">
+      <c r="AH38" s="2">
         <v>43465</v>
       </c>
     </row>
-    <row r="39" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3404,8 +3489,9 @@
       <c r="AE39" s="3"/>
       <c r="AF39" s="3"/>
       <c r="AG39" s="3"/>
-    </row>
-    <row r="40" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH39" s="3"/>
+    </row>
+    <row r="40" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3439,863 +3525,891 @@
       <c r="AE40" s="3"/>
       <c r="AF40" s="3"/>
       <c r="AG40" s="3"/>
-    </row>
-    <row r="41" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH40" s="3"/>
+    </row>
+    <row r="41" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>516800</v>
+      </c>
+      <c r="E41" s="3">
         <v>770900</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>655500</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>689300</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>549600</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>495400</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>526900</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>420100</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>380300</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>395700</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>634300</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>722600</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>636100</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>702100</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>458100</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>424100</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>240200</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>823100</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>1055300</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>819200</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>726000</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>508200</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>504000</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>413900</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>605800</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3">
         <v>284000</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AD41" s="3">
         <v>422000</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AE41" s="3">
         <v>164300</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AF41" s="3">
         <v>118100</v>
       </c>
-      <c r="AF41" s="3">
+      <c r="AG41" s="3">
         <v>171200</v>
       </c>
-      <c r="AG41" s="3">
+      <c r="AH41" s="3">
         <v>201300</v>
       </c>
     </row>
-    <row r="42" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>357600</v>
+      </c>
+      <c r="E42" s="3">
         <v>354500</v>
       </c>
-      <c r="E42" s="3">
+      <c r="F42" s="3">
         <v>412900</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>535700</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>455000</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>433700</v>
       </c>
-      <c r="I42" s="3">
+      <c r="J42" s="3">
         <v>393600</v>
       </c>
-      <c r="J42" s="3">
+      <c r="K42" s="3">
         <v>375600</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>216300</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>276400</v>
       </c>
-      <c r="M42" s="3">
+      <c r="N42" s="3">
         <v>403600</v>
       </c>
-      <c r="N42" s="3">
+      <c r="O42" s="3">
         <v>167700</v>
       </c>
-      <c r="O42" s="3">
+      <c r="P42" s="3">
         <v>56300</v>
       </c>
-      <c r="P42" s="3">
+      <c r="Q42" s="3">
         <v>64300</v>
       </c>
-      <c r="Q42" s="3">
+      <c r="R42" s="3">
         <v>393700</v>
       </c>
-      <c r="R42" s="3">
+      <c r="S42" s="3">
         <v>260000</v>
       </c>
-      <c r="S42" s="3">
+      <c r="T42" s="3">
         <v>218000</v>
       </c>
-      <c r="T42" s="3">
+      <c r="U42" s="3">
         <v>837500</v>
       </c>
-      <c r="U42" s="3">
+      <c r="V42" s="3">
         <v>922000</v>
       </c>
-      <c r="V42" s="3">
+      <c r="W42" s="3">
         <v>665600</v>
       </c>
-      <c r="W42" s="3">
+      <c r="X42" s="3">
         <v>653600</v>
       </c>
-      <c r="X42" s="3">
+      <c r="Y42" s="3">
         <v>299700</v>
       </c>
-      <c r="Y42" s="3">
+      <c r="Z42" s="3">
         <v>405200</v>
       </c>
-      <c r="Z42" s="3">
+      <c r="AA42" s="3">
         <v>294700</v>
       </c>
-      <c r="AA42" s="3">
+      <c r="AB42" s="3">
         <v>50300</v>
       </c>
-      <c r="AB42" s="3">
+      <c r="AC42" s="3">
         <v>7000</v>
       </c>
-      <c r="AC42" s="3">
+      <c r="AD42" s="3">
         <v>120900</v>
       </c>
-      <c r="AD42" s="3">
+      <c r="AE42" s="3">
         <v>146700</v>
       </c>
-      <c r="AE42" s="3">
+      <c r="AF42" s="3">
         <v>87400</v>
       </c>
-      <c r="AF42" s="3">
+      <c r="AG42" s="3">
         <v>140900</v>
       </c>
-      <c r="AG42" s="3">
+      <c r="AH42" s="3">
         <v>146900</v>
       </c>
     </row>
-    <row r="43" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>1185400</v>
+      </c>
+      <c r="E43" s="3">
         <v>1219500</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>1115400</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>1140100</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>1165400</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>1047600</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>932800</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>1020200</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>1001700</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>1073200</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>1083800</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>1020000</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>952500</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>915100</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>829300</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>816200</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>958900</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>898400</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>955400</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>875900</v>
       </c>
-      <c r="W43" s="3">
+      <c r="X43" s="3">
         <v>867400</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Y43" s="3">
         <v>843400</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="Z43" s="3">
         <v>948600</v>
       </c>
-      <c r="Z43" s="3">
+      <c r="AA43" s="3">
         <v>956400</v>
       </c>
-      <c r="AA43" s="3">
+      <c r="AB43" s="3">
         <v>849600</v>
       </c>
-      <c r="AB43" s="3">
+      <c r="AC43" s="3">
         <v>835500</v>
       </c>
-      <c r="AC43" s="3">
+      <c r="AD43" s="3">
         <v>923500</v>
       </c>
-      <c r="AD43" s="3">
+      <c r="AE43" s="3">
         <v>785800</v>
       </c>
-      <c r="AE43" s="3">
+      <c r="AF43" s="3">
         <v>661200</v>
       </c>
-      <c r="AF43" s="3">
+      <c r="AG43" s="3">
         <v>670700</v>
       </c>
-      <c r="AG43" s="3">
+      <c r="AH43" s="3">
         <v>648700</v>
       </c>
     </row>
-    <row r="44" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>82500</v>
+      </c>
+      <c r="E44" s="3">
         <v>74300</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>64900</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>66300</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>65700</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>57500</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>47500</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>70200</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>74900</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>80700</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>68400</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>83200</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>77700</v>
       </c>
-      <c r="P44" s="3">
+      <c r="Q44" s="3">
         <v>59500</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="R44" s="3">
         <v>42400</v>
       </c>
-      <c r="R44" s="3">
+      <c r="S44" s="3">
         <v>51400</v>
       </c>
-      <c r="S44" s="3">
+      <c r="T44" s="3">
         <v>56100</v>
       </c>
-      <c r="T44" s="3">
+      <c r="U44" s="3">
         <v>45700</v>
       </c>
-      <c r="U44" s="3">
+      <c r="V44" s="3">
         <v>40900</v>
       </c>
-      <c r="V44" s="3">
+      <c r="W44" s="3">
         <v>46600</v>
       </c>
-      <c r="W44" s="3">
+      <c r="X44" s="3">
         <v>43700</v>
       </c>
-      <c r="X44" s="3">
+      <c r="Y44" s="3">
         <v>56300</v>
       </c>
-      <c r="Y44" s="3">
+      <c r="Z44" s="3">
         <v>48300</v>
       </c>
-      <c r="Z44" s="3">
+      <c r="AA44" s="3">
         <v>40300</v>
       </c>
-      <c r="AA44" s="3">
+      <c r="AB44" s="3">
         <v>40100</v>
       </c>
-      <c r="AB44" s="3">
+      <c r="AC44" s="3">
         <v>47900</v>
       </c>
-      <c r="AC44" s="3">
+      <c r="AD44" s="3">
         <v>37500</v>
       </c>
-      <c r="AD44" s="3">
+      <c r="AE44" s="3">
         <v>39600</v>
       </c>
-      <c r="AE44" s="3">
+      <c r="AF44" s="3">
         <v>37800</v>
       </c>
-      <c r="AF44" s="3">
+      <c r="AG44" s="3">
         <v>40200</v>
       </c>
-      <c r="AG44" s="3">
+      <c r="AH44" s="3">
         <v>34300</v>
       </c>
     </row>
-    <row r="45" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>124600</v>
+      </c>
+      <c r="E45" s="3">
         <v>137800</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>136100</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>128300</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>129300</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>111700</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>101300</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>105700</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>110600</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>112600</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>111100</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>103300</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>102500</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>91300</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>139300</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>174200</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>279700</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>192100</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>134300</v>
       </c>
-      <c r="V45" s="3">
+      <c r="W45" s="3">
         <v>132600</v>
       </c>
-      <c r="W45" s="3">
+      <c r="X45" s="3">
         <v>170200</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Y45" s="3">
         <v>172100</v>
       </c>
-      <c r="Y45" s="3">
+      <c r="Z45" s="3">
         <v>131600</v>
       </c>
-      <c r="Z45" s="3">
+      <c r="AA45" s="3">
         <v>164900</v>
       </c>
-      <c r="AA45" s="3">
+      <c r="AB45" s="3">
         <v>101300</v>
       </c>
-      <c r="AB45" s="3">
+      <c r="AC45" s="3">
         <v>108500</v>
       </c>
-      <c r="AC45" s="3">
+      <c r="AD45" s="3">
         <v>57500</v>
       </c>
-      <c r="AD45" s="3">
+      <c r="AE45" s="3">
         <v>121800</v>
       </c>
-      <c r="AE45" s="3">
+      <c r="AF45" s="3">
         <v>152000</v>
       </c>
-      <c r="AF45" s="3">
+      <c r="AG45" s="3">
         <v>206800</v>
       </c>
-      <c r="AG45" s="3">
+      <c r="AH45" s="3">
         <v>91300</v>
       </c>
     </row>
-    <row r="46" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>2392300</v>
+      </c>
+      <c r="E46" s="3">
         <v>2700200</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>2444500</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>2643100</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>2469400</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>2260900</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>2047400</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>2066300</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>1872900</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>2060500</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>2350300</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>2169900</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>1924800</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>1955800</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>1862800</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>1725900</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>1752900</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>2796900</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>3107900</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>2539900</v>
       </c>
-      <c r="W46" s="3">
+      <c r="X46" s="3">
         <v>2460900</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Y46" s="3">
         <v>1879800</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="Z46" s="3">
         <v>2037500</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AA46" s="3">
         <v>1870100</v>
       </c>
-      <c r="AA46" s="3">
+      <c r="AB46" s="3">
         <v>1647200</v>
       </c>
-      <c r="AB46" s="3">
+      <c r="AC46" s="3">
         <v>1283000</v>
       </c>
-      <c r="AC46" s="3">
+      <c r="AD46" s="3">
         <v>1561500</v>
       </c>
-      <c r="AD46" s="3">
+      <c r="AE46" s="3">
         <v>1258200</v>
       </c>
-      <c r="AE46" s="3">
+      <c r="AF46" s="3">
         <v>1056500</v>
       </c>
-      <c r="AF46" s="3">
+      <c r="AG46" s="3">
         <v>1229800</v>
       </c>
-      <c r="AG46" s="3">
+      <c r="AH46" s="3">
         <v>1122400</v>
       </c>
     </row>
-    <row r="47" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>70200</v>
+      </c>
+      <c r="E47" s="3">
         <v>305600</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>295100</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>306700</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>306500</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>285100</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>258000</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>292800</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>281000</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>330100</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>346300</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>330900</v>
       </c>
-      <c r="O47" s="3">
+      <c r="P47" s="3">
         <v>347400</v>
       </c>
-      <c r="P47" s="3">
+      <c r="Q47" s="3">
         <v>303100</v>
       </c>
-      <c r="Q47" s="3">
+      <c r="R47" s="3">
         <v>576000</v>
       </c>
-      <c r="R47" s="3">
+      <c r="S47" s="3">
         <v>637900</v>
       </c>
-      <c r="S47" s="3">
+      <c r="T47" s="3">
         <v>683700</v>
       </c>
-      <c r="T47" s="3">
+      <c r="U47" s="3">
         <v>698500</v>
       </c>
-      <c r="U47" s="3">
+      <c r="V47" s="3">
         <v>693400</v>
       </c>
-      <c r="V47" s="3">
+      <c r="W47" s="3">
         <v>411600</v>
       </c>
-      <c r="W47" s="3">
+      <c r="X47" s="3">
         <v>334300</v>
       </c>
-      <c r="X47" s="3">
+      <c r="Y47" s="3">
         <v>367500</v>
       </c>
-      <c r="Y47" s="3">
+      <c r="Z47" s="3">
         <v>444200</v>
       </c>
-      <c r="Z47" s="3">
+      <c r="AA47" s="3">
         <v>410400</v>
       </c>
-      <c r="AA47" s="3">
+      <c r="AB47" s="3">
         <v>665000</v>
       </c>
-      <c r="AB47" s="3">
+      <c r="AC47" s="3">
         <v>603700</v>
       </c>
-      <c r="AC47" s="3">
+      <c r="AD47" s="3">
         <v>609100</v>
       </c>
-      <c r="AD47" s="3">
+      <c r="AE47" s="3">
         <v>786100</v>
       </c>
-      <c r="AE47" s="3">
+      <c r="AF47" s="3">
         <v>766800</v>
       </c>
-      <c r="AF47" s="3">
+      <c r="AG47" s="3">
         <v>294700</v>
       </c>
-      <c r="AG47" s="3">
+      <c r="AH47" s="3">
         <v>300500</v>
       </c>
     </row>
-    <row r="48" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>4705100</v>
+      </c>
+      <c r="E48" s="3">
         <v>4474700</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>4225000</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>4355000</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>4285800</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>4039500</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>3705800</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>4145800</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>4085600</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>4545300</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>4641600</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>4553300</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>4811700</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>4629200</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>4072900</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>4268300</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>4739300</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>3963300</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>3695400</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>3515000</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>3373600</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>3450400</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="Z48" s="3">
         <v>3542300</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AA48" s="3">
         <v>3380900</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AB48" s="3">
         <v>3415200</v>
       </c>
-      <c r="AB48" s="3">
+      <c r="AC48" s="3">
         <v>3190900</v>
       </c>
-      <c r="AC48" s="3">
+      <c r="AD48" s="3">
         <v>3253000</v>
       </c>
-      <c r="AD48" s="3">
+      <c r="AE48" s="3">
         <v>3129600</v>
       </c>
-      <c r="AE48" s="3">
+      <c r="AF48" s="3">
         <v>2907800</v>
       </c>
-      <c r="AF48" s="3">
+      <c r="AG48" s="3">
         <v>2970000</v>
       </c>
-      <c r="AG48" s="3">
+      <c r="AH48" s="3">
         <v>2096500</v>
       </c>
     </row>
-    <row r="49" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>2969300</v>
+      </c>
+      <c r="E49" s="3">
         <v>2808300</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>2631200</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>2704500</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>2666000</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>2566900</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>2384900</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>2720700</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>2717100</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>3059400</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>3197400</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>3135700</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>3304700</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>3204000</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>2950500</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>2946800</v>
       </c>
-      <c r="S49" s="3">
+      <c r="T49" s="3">
         <v>3155600</v>
       </c>
-      <c r="T49" s="3">
+      <c r="U49" s="3">
         <v>2179800</v>
       </c>
-      <c r="U49" s="3">
+      <c r="V49" s="3">
         <v>2136500</v>
       </c>
-      <c r="V49" s="3">
+      <c r="W49" s="3">
         <v>1459200</v>
       </c>
-      <c r="W49" s="3">
+      <c r="X49" s="3">
         <v>1444800</v>
       </c>
-      <c r="X49" s="3">
+      <c r="Y49" s="3">
         <v>1650300</v>
       </c>
-      <c r="Y49" s="3">
+      <c r="Z49" s="3">
         <v>1766600</v>
       </c>
-      <c r="Z49" s="3">
+      <c r="AA49" s="3">
         <v>1755400</v>
       </c>
-      <c r="AA49" s="3">
+      <c r="AB49" s="3">
         <v>1826000</v>
       </c>
-      <c r="AB49" s="3">
+      <c r="AC49" s="3">
         <v>1703000</v>
       </c>
-      <c r="AC49" s="3">
+      <c r="AD49" s="3">
         <v>1785700</v>
       </c>
-      <c r="AD49" s="3">
+      <c r="AE49" s="3">
         <v>1846400</v>
       </c>
-      <c r="AE49" s="3">
+      <c r="AF49" s="3">
         <v>1791600</v>
       </c>
-      <c r="AF49" s="3">
+      <c r="AG49" s="3">
         <v>1947200</v>
       </c>
-      <c r="AG49" s="3">
+      <c r="AH49" s="3">
         <v>1998900</v>
       </c>
     </row>
-    <row r="50" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4389,8 +4503,11 @@
       <c r="AG50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4484,103 +4601,109 @@
       <c r="AG51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>473000</v>
+      </c>
+      <c r="E52" s="3">
         <v>462800</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>434300</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>444300</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>431800</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>401300</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>480500</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>522500</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>498500</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>505200</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>510200</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>651400</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>805600</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>728200</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>676000</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>525300</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>552700</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>442800</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>422300</v>
       </c>
-      <c r="V52" s="3">
+      <c r="W52" s="3">
         <v>931700</v>
       </c>
-      <c r="W52" s="3">
+      <c r="X52" s="3">
         <v>878600</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Y52" s="3">
         <v>344500</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="Z52" s="3">
         <v>361100</v>
       </c>
-      <c r="Z52" s="3">
+      <c r="AA52" s="3">
         <v>333500</v>
       </c>
-      <c r="AA52" s="3">
+      <c r="AB52" s="3">
         <v>295600</v>
       </c>
-      <c r="AB52" s="3">
+      <c r="AC52" s="3">
         <v>270900</v>
       </c>
-      <c r="AC52" s="3">
+      <c r="AD52" s="3">
         <v>243100</v>
       </c>
-      <c r="AD52" s="3">
+      <c r="AE52" s="3">
         <v>278500</v>
       </c>
-      <c r="AE52" s="3">
+      <c r="AF52" s="3">
         <v>276200</v>
       </c>
-      <c r="AF52" s="3">
+      <c r="AG52" s="3">
         <v>448900</v>
       </c>
-      <c r="AG52" s="3">
+      <c r="AH52" s="3">
         <v>461900</v>
       </c>
     </row>
-    <row r="53" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -4674,103 +4797,109 @@
       <c r="AG53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>11038900</v>
+      </c>
+      <c r="E54" s="3">
         <v>11079000</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>10337500</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>10765100</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>10452700</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>9847200</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>9107200</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>10015400</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>9733200</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>10833300</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>11388400</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>11207800</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>11553300</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>11176600</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>10138300</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>10104100</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>10884200</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>10081300</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>10055500</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>8857300</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>8492200</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>7692600</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>8151800</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>7750300</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>7849100</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>7051500</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3">
         <v>7452400</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AE54" s="3">
         <v>7298800</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AF54" s="3">
         <v>6798900</v>
       </c>
-      <c r="AF54" s="3">
+      <c r="AG54" s="3">
         <v>6890500</v>
       </c>
-      <c r="AG54" s="3">
+      <c r="AH54" s="3">
         <v>5980300</v>
       </c>
     </row>
-    <row r="55" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -4804,8 +4933,9 @@
       <c r="AE55" s="3"/>
       <c r="AF55" s="3"/>
       <c r="AG55" s="3"/>
-    </row>
-    <row r="56" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH55" s="3"/>
+    </row>
+    <row r="56" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -4839,578 +4969,597 @@
       <c r="AE56" s="3"/>
       <c r="AF56" s="3"/>
       <c r="AG56" s="3"/>
-    </row>
-    <row r="57" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH56" s="3"/>
+    </row>
+    <row r="57" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>934500</v>
+      </c>
+      <c r="E57" s="3">
         <v>992800</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>933000</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>792100</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>830000</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>790600</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>806300</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>671000</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>657300</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>780000</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>950500</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>771700</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>757200</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>762900</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>761600</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>766200</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>818400</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>618900</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>659500</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>534400</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>501500</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Y57" s="3">
         <v>497900</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="Z57" s="3">
         <v>612300</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AA57" s="3">
         <v>423900</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AB57" s="3">
         <v>407700</v>
       </c>
-      <c r="AB57" s="3">
+      <c r="AC57" s="3">
         <v>470400</v>
       </c>
-      <c r="AC57" s="3">
+      <c r="AD57" s="3">
         <v>724600</v>
       </c>
-      <c r="AD57" s="3">
+      <c r="AE57" s="3">
         <v>548300</v>
       </c>
-      <c r="AE57" s="3">
+      <c r="AF57" s="3">
         <v>512000</v>
       </c>
-      <c r="AF57" s="3">
+      <c r="AG57" s="3">
         <v>707700</v>
       </c>
-      <c r="AG57" s="3">
+      <c r="AH57" s="3">
         <v>809000</v>
       </c>
     </row>
-    <row r="58" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>537100</v>
+      </c>
+      <c r="E58" s="3">
         <v>502900</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>477200</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>480500</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>467700</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>334200</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>319800</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>404800</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>402400</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>519900</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>633900</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>839000</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>887000</v>
       </c>
-      <c r="P58" s="3">
+      <c r="Q58" s="3">
         <v>767500</v>
       </c>
-      <c r="Q58" s="3">
+      <c r="R58" s="3">
         <v>633000</v>
       </c>
-      <c r="R58" s="3">
+      <c r="S58" s="3">
         <v>369800</v>
       </c>
-      <c r="S58" s="3">
+      <c r="T58" s="3">
         <v>390000</v>
       </c>
-      <c r="T58" s="3">
+      <c r="U58" s="3">
         <v>277400</v>
       </c>
-      <c r="U58" s="3">
+      <c r="V58" s="3">
         <v>365000</v>
       </c>
-      <c r="V58" s="3">
+      <c r="W58" s="3">
         <v>359000</v>
       </c>
-      <c r="W58" s="3">
+      <c r="X58" s="3">
         <v>509600</v>
       </c>
-      <c r="X58" s="3">
+      <c r="Y58" s="3">
         <v>630200</v>
       </c>
-      <c r="Y58" s="3">
+      <c r="Z58" s="3">
         <v>537000</v>
       </c>
-      <c r="Z58" s="3">
+      <c r="AA58" s="3">
         <v>543200</v>
       </c>
-      <c r="AA58" s="3">
+      <c r="AB58" s="3">
         <v>513900</v>
       </c>
-      <c r="AB58" s="3">
+      <c r="AC58" s="3">
         <v>363300</v>
       </c>
-      <c r="AC58" s="3">
+      <c r="AD58" s="3">
         <v>416900</v>
       </c>
-      <c r="AD58" s="3">
+      <c r="AE58" s="3">
         <v>432400</v>
       </c>
-      <c r="AE58" s="3">
+      <c r="AF58" s="3">
         <v>233000</v>
       </c>
-      <c r="AF58" s="3">
+      <c r="AG58" s="3">
         <v>249900</v>
       </c>
-      <c r="AG58" s="3">
+      <c r="AH58" s="3">
         <v>169100</v>
       </c>
     </row>
-    <row r="59" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>244800</v>
+      </c>
+      <c r="E59" s="3">
         <v>401500</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>402500</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>544900</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>587700</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>661600</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>262000</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>324000</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>381700</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>533300</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>362800</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>506000</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>497600</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>561400</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>963100</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>771900</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>730500</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>900400</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>1117300</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>482200</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>462100</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>350500</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>475400</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AA59" s="3">
         <v>332200</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AB59" s="3">
         <v>307800</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AC59" s="3">
         <v>229800</v>
       </c>
-      <c r="AC59" s="3">
+      <c r="AD59" s="3">
         <v>357800</v>
       </c>
-      <c r="AD59" s="3">
+      <c r="AE59" s="3">
         <v>383300</v>
       </c>
-      <c r="AE59" s="3">
+      <c r="AF59" s="3">
         <v>256100</v>
       </c>
-      <c r="AF59" s="3">
+      <c r="AG59" s="3">
         <v>261700</v>
       </c>
-      <c r="AG59" s="3">
+      <c r="AH59" s="3">
         <v>345900</v>
       </c>
     </row>
-    <row r="60" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>2818200</v>
+      </c>
+      <c r="E60" s="3">
         <v>2948400</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>2759800</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>2754300</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>2726800</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>2569800</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>2074000</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>2135000</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>2117900</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>2546700</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>2655000</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>2747000</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>2750300</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>2640200</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>2357700</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>1907900</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>1938900</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>1796700</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>2141800</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>1375500</v>
       </c>
-      <c r="W60" s="3">
+      <c r="X60" s="3">
         <v>1473300</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Y60" s="3">
         <v>1478600</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="Z60" s="3">
         <v>1624700</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AA60" s="3">
         <v>1299200</v>
       </c>
-      <c r="AA60" s="3">
+      <c r="AB60" s="3">
         <v>1229400</v>
       </c>
-      <c r="AB60" s="3">
+      <c r="AC60" s="3">
         <v>1063500</v>
       </c>
-      <c r="AC60" s="3">
+      <c r="AD60" s="3">
         <v>1499300</v>
       </c>
-      <c r="AD60" s="3">
+      <c r="AE60" s="3">
         <v>1364000</v>
       </c>
-      <c r="AE60" s="3">
+      <c r="AF60" s="3">
         <v>1001100</v>
       </c>
-      <c r="AF60" s="3">
+      <c r="AG60" s="3">
         <v>1219300</v>
       </c>
-      <c r="AG60" s="3">
+      <c r="AH60" s="3">
         <v>1324000</v>
       </c>
     </row>
-    <row r="61" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>2647200</v>
+      </c>
+      <c r="E61" s="3">
         <v>2706000</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>2526300</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>2589300</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>2509800</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>2420700</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>2204300</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>2467900</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>2403200</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>2598700</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>2669200</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>2653700</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>2823500</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>2816500</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>2566500</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>2847800</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>3116100</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>2431100</v>
       </c>
-      <c r="U61" s="3">
+      <c r="V61" s="3">
         <v>2240600</v>
       </c>
-      <c r="V61" s="3">
+      <c r="W61" s="3">
         <v>2043100</v>
       </c>
-      <c r="W61" s="3">
+      <c r="X61" s="3">
         <v>1939900</v>
       </c>
-      <c r="X61" s="3">
+      <c r="Y61" s="3">
         <v>1417100</v>
       </c>
-      <c r="Y61" s="3">
+      <c r="Z61" s="3">
         <v>1561600</v>
       </c>
-      <c r="Z61" s="3">
+      <c r="AA61" s="3">
         <v>1494800</v>
       </c>
-      <c r="AA61" s="3">
+      <c r="AB61" s="3">
         <v>1638000</v>
       </c>
-      <c r="AB61" s="3">
+      <c r="AC61" s="3">
         <v>1534300</v>
       </c>
-      <c r="AC61" s="3">
+      <c r="AD61" s="3">
         <v>1395000</v>
       </c>
-      <c r="AD61" s="3">
+      <c r="AE61" s="3">
         <v>1393500</v>
       </c>
-      <c r="AE61" s="3">
+      <c r="AF61" s="3">
         <v>1461300</v>
       </c>
-      <c r="AF61" s="3">
+      <c r="AG61" s="3">
         <v>1503800</v>
       </c>
-      <c r="AG61" s="3">
+      <c r="AH61" s="3">
         <v>505100</v>
       </c>
     </row>
-    <row r="62" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>670400</v>
+      </c>
+      <c r="E62" s="3">
         <v>663600</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>605500</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>593400</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>507200</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>495900</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>468800</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>536300</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>516200</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>575800</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>573500</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>559600</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>593200</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>610100</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>649500</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>674800</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>752300</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>643300</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>605500</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>475800</v>
       </c>
-      <c r="W62" s="3">
+      <c r="X62" s="3">
         <v>475600</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Y62" s="3">
         <v>407100</v>
       </c>
-      <c r="Y62" s="3">
+      <c r="Z62" s="3">
         <v>428600</v>
       </c>
-      <c r="Z62" s="3">
+      <c r="AA62" s="3">
         <v>427700</v>
       </c>
-      <c r="AA62" s="3">
+      <c r="AB62" s="3">
         <v>479400</v>
       </c>
-      <c r="AB62" s="3">
+      <c r="AC62" s="3">
         <v>421400</v>
       </c>
-      <c r="AC62" s="3">
+      <c r="AD62" s="3">
         <v>415000</v>
       </c>
-      <c r="AD62" s="3">
+      <c r="AE62" s="3">
         <v>459000</v>
       </c>
-      <c r="AE62" s="3">
+      <c r="AF62" s="3">
         <v>451600</v>
       </c>
-      <c r="AF62" s="3">
+      <c r="AG62" s="3">
         <v>440000</v>
       </c>
-      <c r="AG62" s="3">
+      <c r="AH62" s="3">
         <v>446900</v>
       </c>
     </row>
-    <row r="63" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -5504,8 +5653,11 @@
       <c r="AG63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -5599,8 +5751,11 @@
       <c r="AG64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -5694,103 +5849,109 @@
       <c r="AG65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>6210400</v>
+      </c>
+      <c r="E66" s="3">
         <v>6397900</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>5984300</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>6034100</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>5841500</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>5581800</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>4838000</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>5244700</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>5144300</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>5843700</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>6026900</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>6087000</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>6300600</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>6196700</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>5573600</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>5430500</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>5807300</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>4871000</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>4987900</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>3894400</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>3888700</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>3302800</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>3614900</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>3221800</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>3346700</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>3019200</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AD66" s="3">
         <v>3309300</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AE66" s="3">
         <v>3216600</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AF66" s="3">
         <v>2914000</v>
       </c>
-      <c r="AF66" s="3">
+      <c r="AG66" s="3">
         <v>3163100</v>
       </c>
-      <c r="AG66" s="3">
+      <c r="AH66" s="3">
         <v>2276100</v>
       </c>
     </row>
-    <row r="67" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -5824,8 +5985,9 @@
       <c r="AE67" s="3"/>
       <c r="AF67" s="3"/>
       <c r="AG67" s="3"/>
-    </row>
-    <row r="68" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH67" s="3"/>
+    </row>
+    <row r="68" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -5919,8 +6081,11 @@
       <c r="AG68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -6014,8 +6179,11 @@
       <c r="AG69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -6109,8 +6277,11 @@
       <c r="AG70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -6204,103 +6375,109 @@
       <c r="AG71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>2164500</v>
+      </c>
+      <c r="E72" s="3">
         <v>2037800</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>1850500</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>2194800</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>2072500</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>1851800</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>2030700</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>2235000</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>2098600</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>2227000</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>2506000</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>2347700</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>2371300</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>2237100</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>2079500</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>2119200</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>2311700</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>2368000</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>2277700</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>2179300</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>1930100</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>1803500</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>1831900</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>1835100</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>2161300</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AC72" s="3">
         <v>2204900</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AD72" s="3">
         <v>2251400</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AE72" s="3">
         <v>2160900</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AF72" s="3">
         <v>2071600</v>
       </c>
-      <c r="AF72" s="3">
+      <c r="AG72" s="3">
         <v>1811200</v>
       </c>
-      <c r="AG72" s="3">
+      <c r="AH72" s="3">
         <v>1788100</v>
       </c>
     </row>
-    <row r="73" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -6394,8 +6571,11 @@
       <c r="AG73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -6489,8 +6669,11 @@
       <c r="AG74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -6584,103 +6767,109 @@
       <c r="AG75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>4828500</v>
+      </c>
+      <c r="E76" s="3">
         <v>4681100</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>4353200</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>4731000</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>4611200</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>4265400</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>4269200</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>4770700</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>4588900</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>4989600</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>5361600</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>5120900</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>5252700</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>4979900</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>4564700</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>4673600</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>5076900</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>5210200</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>5067600</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>4962900</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>4603400</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>4389800</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>4536900</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>4528500</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>4502400</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>4032300</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AD76" s="3">
         <v>4143200</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AE76" s="3">
         <v>4082200</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AF76" s="3">
         <v>3884900</v>
       </c>
-      <c r="AF76" s="3">
+      <c r="AG76" s="3">
         <v>3727500</v>
       </c>
-      <c r="AG76" s="3">
+      <c r="AH76" s="3">
         <v>3704200</v>
       </c>
     </row>
-    <row r="77" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -6774,203 +6963,212 @@
       <c r="AG77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:34" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E80" s="2">
         <v>46112</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>46022</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45930</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45838</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45747</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45657</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45565</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45473</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>45382</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>45291</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>45199</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>45107</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>45016</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44926</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44834</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44742</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44651</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>44561</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>44469</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>44377</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>44286</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>44196</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>44104</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>44012</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43921</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43830</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>43738</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>43646</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AG80" s="2">
         <v>43555</v>
       </c>
-      <c r="AG80" s="2">
+      <c r="AH80" s="2">
         <v>43465</v>
       </c>
     </row>
-    <row r="81" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>187100</v>
+      </c>
+      <c r="E81" s="3">
         <v>156600</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>241700</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>226600</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>179000</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>139100</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>169500</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>147800</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>140700</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>103600</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>223100</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>143400</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>129900</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>81500</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>96700</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>82700</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>56000</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>83400</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>204900</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>199900</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>130200</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>51800</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>198300</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>76000</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>86800</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>28900</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>169600</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AE81" s="3">
         <v>105400</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AF81" s="3">
         <v>358100</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AG81" s="3">
         <v>22500</v>
       </c>
-      <c r="AG81" s="3">
+      <c r="AH81" s="3">
         <v>118300</v>
       </c>
     </row>
-    <row r="82" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -7004,103 +7202,107 @@
       <c r="AE82" s="3"/>
       <c r="AF82" s="3"/>
       <c r="AG82" s="3"/>
-    </row>
-    <row r="83" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH82" s="3"/>
+    </row>
+    <row r="83" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>236000</v>
+      </c>
+      <c r="E83" s="3">
         <v>220900</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>201700</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>241100</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>229400</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>254400</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>261100</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>253800</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>283000</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>255300</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>135300</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>260700</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>233500</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>205100</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>334000</v>
       </c>
-      <c r="R83" s="3">
+      <c r="S83" s="3">
         <v>347400</v>
       </c>
-      <c r="S83" s="3">
+      <c r="T83" s="3">
         <v>338600</v>
       </c>
-      <c r="T83" s="3">
+      <c r="U83" s="3">
         <v>287700</v>
       </c>
-      <c r="U83" s="3">
+      <c r="V83" s="3">
         <v>289800</v>
       </c>
-      <c r="V83" s="3">
+      <c r="W83" s="3">
         <v>282800</v>
       </c>
-      <c r="W83" s="3">
+      <c r="X83" s="3">
         <v>275700</v>
       </c>
-      <c r="X83" s="3">
+      <c r="Y83" s="3">
         <v>267100</v>
       </c>
-      <c r="Y83" s="3">
+      <c r="Z83" s="3">
         <v>269800</v>
       </c>
-      <c r="Z83" s="3">
+      <c r="AA83" s="3">
         <v>270800</v>
       </c>
-      <c r="AA83" s="3">
+      <c r="AB83" s="3">
         <v>543500</v>
       </c>
-      <c r="AB83" s="3">
+      <c r="AC83" s="3">
         <v>251500</v>
       </c>
-      <c r="AC83" s="3">
+      <c r="AD83" s="3">
         <v>195800</v>
       </c>
-      <c r="AD83" s="3">
+      <c r="AE83" s="3">
         <v>269500</v>
       </c>
-      <c r="AE83" s="3">
+      <c r="AF83" s="3">
         <v>229800</v>
       </c>
-      <c r="AF83" s="3">
+      <c r="AG83" s="3">
         <v>249700</v>
       </c>
-      <c r="AG83" s="3">
+      <c r="AH83" s="3">
         <v>190500</v>
       </c>
     </row>
-    <row r="84" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -7194,8 +7396,11 @@
       <c r="AG84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -7289,8 +7494,11 @@
       <c r="AG85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -7384,8 +7592,11 @@
       <c r="AG86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -7479,8 +7690,11 @@
       <c r="AG87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -7574,103 +7788,109 @@
       <c r="AG88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>601300</v>
+      </c>
+      <c r="E89" s="3">
         <v>511100</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>775300</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>694800</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>545200</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>435300</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>731000</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>638700</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>483900</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>328100</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>999300</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>697700</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>441300</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>387000</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>629400</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>641600</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>267500</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>230200</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>630400</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>558400</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>432300</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>364700</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>723800</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>426300</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>549100</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AC89" s="3">
         <v>87000</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AD89" s="3">
         <v>666100</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AE89" s="3">
         <v>394600</v>
       </c>
-      <c r="AE89" s="3">
+      <c r="AF89" s="3">
         <v>187500</v>
       </c>
-      <c r="AF89" s="3">
+      <c r="AG89" s="3">
         <v>55400</v>
       </c>
-      <c r="AG89" s="3">
+      <c r="AH89" s="3">
         <v>546400</v>
       </c>
     </row>
-    <row r="90" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -7704,103 +7924,107 @@
       <c r="AE90" s="3"/>
       <c r="AF90" s="3"/>
       <c r="AG90" s="3"/>
-    </row>
-    <row r="91" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH90" s="3"/>
+    </row>
+    <row r="91" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-180400</v>
+      </c>
+      <c r="E91" s="3">
         <v>-259500</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-244500</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-182700</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-161900</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-233600</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-222200</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-164600</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-166600</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-270100</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-266200</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-199900</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-192000</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-254500</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-1375200</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-977600</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-1049600</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-1328000</v>
       </c>
-      <c r="U91" s="3">
+      <c r="V91" s="3">
         <v>-2157400</v>
       </c>
-      <c r="V91" s="3">
+      <c r="W91" s="3">
         <v>-896500</v>
       </c>
-      <c r="W91" s="3">
+      <c r="X91" s="3">
         <v>-175400</v>
       </c>
-      <c r="X91" s="3">
+      <c r="Y91" s="3">
         <v>-247700</v>
       </c>
-      <c r="Y91" s="3">
+      <c r="Z91" s="3">
         <v>-286500</v>
       </c>
-      <c r="Z91" s="3">
+      <c r="AA91" s="3">
         <v>-165600</v>
       </c>
-      <c r="AA91" s="3">
+      <c r="AB91" s="3">
         <v>-310800</v>
       </c>
-      <c r="AB91" s="3">
+      <c r="AC91" s="3">
         <v>-161400</v>
       </c>
-      <c r="AC91" s="3">
+      <c r="AD91" s="3">
         <v>-246500</v>
       </c>
-      <c r="AD91" s="3">
+      <c r="AE91" s="3">
         <v>-173300</v>
       </c>
-      <c r="AE91" s="3">
+      <c r="AF91" s="3">
         <v>-167300</v>
       </c>
-      <c r="AF91" s="3">
+      <c r="AG91" s="3">
         <v>-121700</v>
       </c>
-      <c r="AG91" s="3">
+      <c r="AH91" s="3">
         <v>-256800</v>
       </c>
     </row>
-    <row r="92" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -7894,8 +8118,11 @@
       <c r="AG92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -7989,103 +8216,109 @@
       <c r="AG93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-333300</v>
+      </c>
+      <c r="E94" s="3">
         <v>-173400</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-33400</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-233300</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-146900</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-232400</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-274500</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-321000</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-139800</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-145900</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-594600</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-309200</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-176900</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>118300</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-396300</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-268300</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-828100</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-170900</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-470600</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>-166300</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>-518500</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>-159800</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Z94" s="3">
         <v>-395400</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AA94" s="3">
         <v>-408500</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AB94" s="3">
         <v>-231700</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AC94" s="3">
         <v>-50600</v>
       </c>
-      <c r="AC94" s="3">
+      <c r="AD94" s="3">
         <v>-222900</v>
       </c>
-      <c r="AD94" s="3">
+      <c r="AE94" s="3">
         <v>-226400</v>
       </c>
-      <c r="AE94" s="3">
+      <c r="AF94" s="3">
         <v>-121600</v>
       </c>
-      <c r="AF94" s="3">
+      <c r="AG94" s="3">
         <v>-114600</v>
       </c>
-      <c r="AG94" s="3">
+      <c r="AH94" s="3">
         <v>-291500</v>
       </c>
     </row>
-    <row r="95" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -8119,103 +8352,107 @@
       <c r="AE95" s="3"/>
       <c r="AF95" s="3"/>
       <c r="AG95" s="3"/>
-    </row>
-    <row r="96" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH95" s="3"/>
+    </row>
+    <row r="96" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
       <c r="D96" s="3">
+        <v>222600</v>
+      </c>
+      <c r="E96" s="3">
         <v>91700</v>
       </c>
-      <c r="E96" s="3">
+      <c r="F96" s="3">
         <v>658200</v>
       </c>
-      <c r="F96" s="3">
+      <c r="G96" s="3">
         <v>20300</v>
       </c>
-      <c r="G96" s="3">
+      <c r="H96" s="3">
         <v>175500</v>
       </c>
-      <c r="H96" s="3">
+      <c r="I96" s="3">
         <v>116900</v>
       </c>
-      <c r="I96" s="3">
+      <c r="J96" s="3">
         <v>221200</v>
       </c>
-      <c r="J96" s="3">
+      <c r="K96" s="3">
         <v>14800</v>
       </c>
-      <c r="K96" s="3">
+      <c r="L96" s="3">
         <v>112800</v>
       </c>
-      <c r="L96" s="3">
+      <c r="M96" s="3">
         <v>128600</v>
       </c>
-      <c r="M96" s="3">
+      <c r="N96" s="3">
         <v>86300</v>
       </c>
-      <c r="N96" s="3">
+      <c r="O96" s="3">
         <v>57200</v>
       </c>
-      <c r="O96" s="3">
+      <c r="P96" s="3">
         <v>169200</v>
       </c>
-      <c r="P96" s="3">
+      <c r="Q96" s="3">
         <v>129300</v>
       </c>
-      <c r="Q96" s="3">
+      <c r="R96" s="3">
         <v>-47800</v>
       </c>
-      <c r="R96" s="3">
+      <c r="S96" s="3">
         <v>-49200</v>
       </c>
-      <c r="S96" s="3">
+      <c r="T96" s="3">
         <v>-38500</v>
       </c>
-      <c r="T96" s="3">
+      <c r="U96" s="3">
         <v>-97700</v>
       </c>
-      <c r="U96" s="3">
+      <c r="V96" s="3">
         <v>-42700</v>
       </c>
-      <c r="V96" s="3">
+      <c r="W96" s="3">
         <v>-59800</v>
       </c>
-      <c r="W96" s="3">
+      <c r="X96" s="3">
         <v>-9300</v>
       </c>
-      <c r="X96" s="3">
+      <c r="Y96" s="3">
         <v>-91000</v>
       </c>
-      <c r="Y96" s="3">
+      <c r="Z96" s="3">
         <v>-108700</v>
       </c>
-      <c r="Z96" s="3">
+      <c r="AA96" s="3">
         <v>-5700</v>
       </c>
-      <c r="AA96" s="3">
+      <c r="AB96" s="3">
         <v>-112000</v>
       </c>
-      <c r="AB96" s="3">
+      <c r="AC96" s="3">
         <v>-101300</v>
       </c>
-      <c r="AC96" s="3">
+      <c r="AD96" s="3">
         <v>-67300</v>
       </c>
-      <c r="AD96" s="3">
+      <c r="AE96" s="3">
         <v>-11800</v>
       </c>
-      <c r="AE96" s="3">
-        <v>0</v>
-      </c>
       <c r="AF96" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG96" s="3">
         <v>-64200</v>
       </c>
-      <c r="AG96" s="3">
+      <c r="AH96" s="3">
         <v>-42700</v>
       </c>
     </row>
-    <row r="97" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -8309,8 +8546,11 @@
       <c r="AG97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -8404,8 +8644,11 @@
       <c r="AG98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -8499,103 +8742,109 @@
       <c r="AG99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-527500</v>
+      </c>
+      <c r="E100" s="3">
         <v>-258800</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-753400</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-334100</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-370000</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-275900</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-299500</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-285300</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-321300</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-400200</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-514100</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-279900</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>-365700</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>-306500</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>-187600</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>-200400</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>30700</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>-311300</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>74500</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>-328000</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>286200</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>-178500</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="Z100" s="3">
         <v>-240200</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AA100" s="3">
         <v>-202700</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AB100" s="3">
         <v>-161800</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AC100" s="3">
         <v>-160300</v>
       </c>
-      <c r="AC100" s="3">
+      <c r="AD100" s="3">
         <v>-183000</v>
       </c>
-      <c r="AD100" s="3">
+      <c r="AE100" s="3">
         <v>-129100</v>
       </c>
-      <c r="AE100" s="3">
+      <c r="AF100" s="3">
         <v>-109800</v>
       </c>
-      <c r="AF100" s="3">
+      <c r="AG100" s="3">
         <v>29200</v>
       </c>
-      <c r="AG100" s="3">
+      <c r="AH100" s="3">
         <v>-175900</v>
       </c>
     </row>
-    <row r="101" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -8638,8 +8887,8 @@
       <c r="P101" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Q101" s="3">
-        <v>0</v>
+      <c r="Q101" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="R101" s="3">
         <v>0</v>
@@ -8689,99 +8938,105 @@
       <c r="AG101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-259500</v>
+      </c>
+      <c r="E102" s="3">
         <v>78900</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-11500</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>127400</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>28300</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-73000</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>157100</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>32400</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>22800</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-218000</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-109400</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>108500</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-101200</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>198800</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>45500</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>202700</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>-562000</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>-252000</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>234300</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>64100</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>199900</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>26400</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>88200</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>-184800</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AB102" s="3">
         <v>155600</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AC102" s="3">
         <v>-123900</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AD102" s="3">
         <v>260200</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AE102" s="3">
         <v>39200</v>
       </c>
-      <c r="AE102" s="3">
+      <c r="AF102" s="3">
         <v>-43900</v>
       </c>
-      <c r="AF102" s="3">
+      <c r="AG102" s="3">
         <v>-30000</v>
       </c>
-      <c r="AG102" s="3">
+      <c r="AH102" s="3">
         <v>79000</v>
       </c>
     </row>
